--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>猫猫</t>
+  </si>
+  <si>
+    <t>愤怒</t>
   </si>
 </sst>
 </file>
@@ -1148,9 +1151,15 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1000</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>

--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -59,9 +59,18 @@
     <t>EntityId</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
     <t>Speed</t>
   </si>
   <si>
+    <t>AtkSpeed</t>
+  </si>
+  <si>
+    <t>CheckRange</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -69,6 +78,9 @@
   </si>
   <si>
     <t>Entity.EntityId</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>##group</t>
@@ -1055,13 +1067,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="15" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,11 +1086,18 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,27 +1107,35 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1116,55 +1143,71 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
+        <v>100</v>
+      </c>
+      <c r="E6" s="2">
         <v>1000</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="F6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>800</v>
+      </c>
+      <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="4"/>
       <c r="B7" s="2">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="E7" s="2">
+        <v>800</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>500</v>
+      </c>
+      <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="4"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1172,8 +1215,9 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="4"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1181,8 +1225,9 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="4"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1190,8 +1235,9 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" s="4"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1199,8 +1245,9 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" s="4"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1208,6 +1255,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,10 +109,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -601,19 +601,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1068,7 +1068,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="15" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="15" customWidth="1"/>
   </cols>
@@ -1175,13 +1175,13 @@
         <v>100</v>
       </c>
       <c r="E6" s="2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -1197,13 +1197,13 @@
         <v>80</v>
       </c>
       <c r="E7" s="2">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -1268,7 +1268,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1280,7 +1280,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -71,6 +71,9 @@
     <t>CheckRange</t>
   </si>
   <si>
+    <t>BulletId</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -98,7 +101,13 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>子弹实体id</t>
+  </si>
+  <si>
     <t>猫猫</t>
+  </si>
+  <si>
+    <t>闪电球</t>
   </si>
   <si>
     <t>愤怒</t>
@@ -109,10 +118,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -601,19 +610,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1068,7 +1077,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="15" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="15" customWidth="1"/>
   </cols>
@@ -1095,7 +1104,9 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -1111,31 +1122,33 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1147,21 +1160,23 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4"/>
@@ -1169,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>100</v>
@@ -1183,7 +1198,9 @@
       <c r="G6" s="2">
         <v>500</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4"/>
@@ -1191,7 +1208,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>80</v>
@@ -1268,7 +1285,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1280,7 +1297,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/角色.xlsx
+++ b/Configs/GameConfig/Datas/角色.xlsx
@@ -107,7 +107,7 @@
     <t>猫猫</t>
   </si>
   <si>
-    <t>闪电球</t>
+    <t>感叹号</t>
   </si>
   <si>
     <t>愤怒</t>
